--- a/stories/arbres/TREE-AUT-030.xlsx
+++ b/stories/arbres/TREE-AUT-030.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Jules est avec maman, dans le salon. Jules a envie de jouer. maman est là, tout près. On va apprendre : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules écoute maman. Jules entend les mots : une étape après l'autre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Jules se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On attend son tour. maman dit : je suis là. On reste ensemble.</t>
+          <t>Jules va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Jules se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On attend son tour. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jules va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Jules se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On attend son tour.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : faire l'étape dite. Jules respire. Jules retient : une étape après l'autre. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2529,6 +2582,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2751,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3753,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3853,6 +3946,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4017,6 +4115,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. La lumière est claire. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4282,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4449,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4616,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4783,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4950,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5117,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5310,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5479,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5646,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5813,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5980,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6147,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6314,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6175,7 +6343,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Jules se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On montre du doigt, sans courir. maman dit : je suis là. On reste ensemble.</t>
+          <t>Jules va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Jules se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6313,6 +6481,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Jules va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Jules se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On montre du doigt, sans courir.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6663,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6836,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : faire l'étape dite. Jules respire. Jules retient : une étape après l'autre. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7027,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7194,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le ballon. Un vélo passe au loin. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7193,6 +7387,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7357,6 +7556,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7723,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7890,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8057,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8224,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8391,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8558,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le seau. La lumière est claire. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8517,6 +8751,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8681,6 +8920,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9087,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9005,6 +9254,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9421,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9329,6 +9588,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9755,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9653,6 +9922,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le doudou. Il y a des miettes sur la table. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9841,6 +10115,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10005,6 +10284,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10451,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10329,6 +10618,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10785,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10653,6 +10952,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11119,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10839,7 +11148,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Jules se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On rit un peu. maman dit : je suis là. On reste ensemble.</t>
+          <t>Jules va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Jules se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On rit un peu. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10977,6 +11286,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Jules va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Jules se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On rit un peu.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11153,6 +11468,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
         </is>
       </c>
     </row>
@@ -11321,6 +11641,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : faire l'étape dite. Jules respire. Jules retient : une étape après l'autre. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11832,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11669,6 +11999,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11857,6 +12192,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12021,6 +12361,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12528,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12345,6 +12695,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12862,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12669,6 +13029,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13196,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12993,6 +13363,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13181,6 +13556,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13345,6 +13725,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13507,6 +13892,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13669,6 +14059,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13831,6 +14226,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13993,6 +14393,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. La couverture est douce. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14155,6 +14560,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14317,6 +14727,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14505,6 +14920,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14669,6 +15089,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14831,6 +15256,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14993,6 +15423,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. La couverture est douce. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15155,6 +15590,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15317,6 +15757,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. On entend un oiseau. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15479,6 +15924,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15497,7 +15947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15570,6 +16020,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-030.xlsx
+++ b/stories/arbres/TREE-AUT-030.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Jules est avec maman, dans le salon. Jules a envie de jouer. maman est là, tout près. On va apprendre : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules écoute maman. Jules entend les mots : une étape après l'autre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Oui. Voici le geste : faire l'étape dite. Jules respire. Jules retient : une étape après l'autre. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|Jules a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2756,6 +2769,7 @@
           <t>narrateur|Jules rejoint Tom. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3105,7 @@
           <t>narrateur|Jules rejoint Léa. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
           <t>narrateur|Jules rejoint Sami. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3758,6 +3777,7 @@
           <t>narrateur|Jules a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3953,6 +3973,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4120,6 +4141,7 @@
           <t>narrateur|Jules rejoint Tom. La lumière est claire. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4287,6 +4309,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4454,6 +4477,7 @@
           <t>narrateur|Jules rejoint Léa. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4621,6 +4645,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4788,6 +4813,7 @@
           <t>narrateur|Jules rejoint Sami. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4955,6 +4981,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5122,6 +5149,7 @@
           <t>narrateur|Jules a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5317,6 +5345,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5484,6 +5513,7 @@
           <t>narrateur|Jules rejoint Tom. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5651,6 +5681,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5818,6 +5849,7 @@
           <t>narrateur|Jules rejoint Léa. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5985,6 +6017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6152,6 +6185,7 @@
           <t>narrateur|Jules rejoint Sami. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6319,6 +6353,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6487,6 +6522,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6670,6 +6706,7 @@
           <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6841,6 +6878,7 @@
           <t>narrateur|Oui. Voici le geste : faire l'étape dite. Jules respire. Jules retient : une étape après l'autre. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7032,6 +7070,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7199,6 +7238,7 @@
           <t>narrateur|Jules a choisi le ballon. Un vélo passe au loin. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7394,6 +7434,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7561,6 +7602,7 @@
           <t>narrateur|Jules rejoint Tom. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7728,6 +7770,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7895,6 +7938,7 @@
           <t>narrateur|Jules rejoint Léa. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8062,6 +8106,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8229,6 +8274,7 @@
           <t>narrateur|Jules rejoint Sami. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8396,6 +8442,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8563,6 +8610,7 @@
           <t>narrateur|Jules a choisi le seau. La lumière est claire. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8758,6 +8806,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8925,6 +8974,7 @@
           <t>narrateur|Jules rejoint Tom. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9092,6 +9142,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9259,6 +9310,7 @@
           <t>narrateur|Jules rejoint Léa. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9426,6 +9478,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9593,6 +9646,7 @@
           <t>narrateur|Jules rejoint Sami. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9760,6 +9814,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9927,6 +9982,7 @@
           <t>narrateur|Jules a choisi le doudou. Il y a des miettes sur la table. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10122,6 +10178,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10289,6 +10346,7 @@
           <t>narrateur|Jules rejoint Tom. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10456,6 +10514,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10623,6 +10682,7 @@
           <t>narrateur|Jules rejoint Léa. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10790,6 +10850,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10957,6 +11018,7 @@
           <t>narrateur|Jules rejoint Sami. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11124,6 +11186,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11292,6 +11355,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11475,6 +11539,7 @@
           <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11646,6 +11711,7 @@
           <t>narrateur|Oui. Voici le geste : faire l'étape dite. Jules respire. Jules retient : une étape après l'autre. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11837,6 +11903,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12004,6 +12071,7 @@
           <t>narrateur|Jules a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12199,6 +12267,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12366,6 +12435,7 @@
           <t>narrateur|Jules rejoint Tom. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12533,6 +12603,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12700,6 +12771,7 @@
           <t>narrateur|Jules rejoint Léa. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12867,6 +12939,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13034,6 +13107,7 @@
           <t>narrateur|Jules rejoint Sami. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13201,6 +13275,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13368,6 +13443,7 @@
           <t>narrateur|Jules a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13563,6 +13639,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13730,6 +13807,7 @@
           <t>narrateur|Jules rejoint Tom. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13897,6 +13975,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14064,6 +14143,7 @@
           <t>narrateur|Jules rejoint Léa. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14231,6 +14311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14398,6 +14479,7 @@
           <t>narrateur|Jules rejoint Sami. La couverture est douce. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14565,6 +14647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14732,6 +14815,7 @@
           <t>narrateur|Jules a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14927,6 +15011,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15094,6 +15179,7 @@
           <t>narrateur|Jules rejoint Tom. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15261,6 +15347,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15428,6 +15515,7 @@
           <t>narrateur|Jules rejoint Léa. La couverture est douce. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15595,6 +15683,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15762,6 +15851,7 @@
           <t>narrateur|Jules rejoint Sami. On entend un oiseau. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15929,6 +16019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15947,7 +16038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16027,6 +16118,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16041,7 +16146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16228,6 +16333,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-030.xlsx
+++ b/stories/arbres/TREE-AUT-030.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Enchaîner le matin — dans le salon</t>
+          <t>La bouilloire et les petits bateaux</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La bouilloire chante dans le salon. Victorino veut déjà le parc. Papa et maman disent : une étape après l'autre. D'abord le matin, ensuite le jeu.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Jules est avec maman, dans le salon. Jules a envie de jouer. maman est là, tout près. On va apprendre : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules écoute maman. Jules entend les mots : une étape après l'autre.</t>
+          <t>La bouilloire chante dans le salon. Elle fait siff, tout aigu. Un rideau à petits bateaux bouge. Un bateau est bleu. Un bateau est jaune. Sur la chaise, une chaussette pend. Elle est encore un peu chaude. Le couloir sent le savon. Un gobelet attend près du lavabo. L'eau est prête, Victorino. Le matin commence, tout doucement. Le tapis du salon a des pois. Un pois rouge. Un pois vert. En ce moment, Victorino a les pieds dessus. Je veux le parc. D'accord. Une étape après l'autre. D'abord le matin. Ensuite le parc. Le manteau attend sur le crochet. Les chaussures attendent près de la porte. On fait l'étape dite. Une étape après l'autre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,7 +1337,30 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Jules est avec maman, dans le salon. Jules a envie de jouer. maman est là, tout près. On va apprendre : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules écoute maman. Jules entend les mots : une étape après l'autre.</t>
+          <t>narrateur|La bouilloire chante dans le salon.
+narrateur|Elle fait siff, tout aigu.
+narrateur|Un rideau à petits bateaux bouge.
+narrateur|Un bateau est bleu.
+narrateur|Un bateau est jaune.
+narrateur|Sur la chaise, une chaussette pend.
+narrateur|Elle est encore un peu chaude.
+narrateur|Le couloir sent le savon.
+narrateur|Un gobelet attend près du lavabo.
+papa|L'eau est prête, Victorino.
+maman|Le matin commence, tout doucement.
+narrateur|Le tapis du salon a des pois.
+narrateur|Un pois rouge.
+narrateur|Un pois vert.
+narrateur|En ce moment, Victorino a les pieds dessus.
+enfant-m|Je veux le parc.
+maman|D'accord.
+maman|Une étape après l'autre.
+papa|D'abord le matin.
+papa|Ensuite le parc.
+narrateur|Le manteau attend sur le crochet.
+narrateur|Les chaussures attendent près de la porte.
+maman|On fait l'étape dite.
+enfant-m|Une étape après l'autre.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1353,7 +1388,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>Ils arrivent au parc. Victorino peut commencer à trois endroits. Le bac à sable, le toboggan, ou les balançoires ? Tu choisis. Ensuite on fait l'étape.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1517,7 +1552,11 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>narrateur|Ils arrivent au parc.
+narrateur|Victorino peut commencer à trois endroits.
+papa|Le bac à sable, le toboggan, ou les balançoires ?
+maman|Tu choisis.
+maman|Ensuite on fait l'étape.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1545,7 +1584,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Jules se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On attend son tour. Je suis là. On reste ensemble.</t>
+          <t>Victorino s'agenouille près du bac à sable. Le sable est frais, un peu humide. Il coule entre ses doigts. Chh. Une petite pelle attend, toute jaune. D'abord le sable. Ensuite on continue. Une étape après l'autre. Je fais un tas. Victorino fait un petit tas rond. Le tas a une ombre, toute courte. Tu as fait l'étape dite. Bravo. Loin, un vélo de boulanger passe. On entend un petit grelot. On reste ensemble, près du bac. Le sable est doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,11 +1724,30 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Jules va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Jules se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On attend son tour.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Victorino s'agenouille près du bac à sable.
+narrateur|Le sable est frais, un peu humide.
+narrateur|Il coule entre ses doigts.
+narrateur|Chh.
+narrateur|Une petite pelle attend, toute jaune.
+papa|D'abord le sable.
+papa|Ensuite on continue.
+maman|Une étape après l'autre.
+enfant-m|Je fais un tas.
+narrateur|Victorino fait un petit tas rond.
+narrateur|Le tas a une ombre, toute courte.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+narrateur|Loin, un vélo de boulanger passe.
+narrateur|On entend un petit grelot.
+maman|On reste ensemble, près du bac.
+enfant-m|Le sable est doux.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1714,7 +1772,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Enchaîner le matin.</t>
+          <t>Victorino se prépare près du bac à sable. On avance comment ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1870,7 +1928,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
+          <t>narrateur|Victorino se prépare près du bac à sable.
+maman|On avance comment ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1898,7 +1957,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : faire l'étape dite. Jules respire. Jules retient : une étape après l'autre. On continue, avec maman.</t>
+          <t>Oui. Une étape après l'autre. Tu as fait l'étape dite. Bravo. Un grain de sable brille sur son genou. Ensuite, on continue. Oui. On continue, avec nous. C'est plus calme, comme ça.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2042,7 +2101,13 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : faire l'étape dite. Jules respire. Jules retient : une étape après l'autre. On continue, avec maman.</t>
+          <t>papa|Oui. Une étape après l'autre.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+narrateur|Un grain de sable brille sur son genou.
+enfant-m|Ensuite, on continue.
+papa|Oui. On continue, avec nous.
+maman|C'est plus calme, comme ça.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2070,7 +2135,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Un objet peut aider le matin, au parc. Le ballon, le seau, ou le doudou ? On prend un objet. Puis l'étape suivante.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2234,7 +2299,10 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Un objet peut aider le matin, au parc.
+papa|Le ballon, le seau, ou le doudou ?
+maman|On prend un objet.
+maman|Puis l'étape suivante.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2262,7 +2330,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
+          <t>Près du bac à sable, le ballon rouge attend. Il est lisse, un peu frais. Le ballon, papa. D'accord. D'abord le tenir. Ensuite rouler. Une étape après l'autre. Victorino pose les deux mains dessus. Le ballon fait un petit bruit de peau. Il le fait rouler tout doux, tout près. Tu as fait l'étape dite. Bravo. Tu as fini de rouler ? Oui. Le sable colle un peu aux chaussures. Le ballon reste à sa place, près de maman.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2402,10 +2470,29 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Près du bac à sable, le ballon rouge attend.
+narrateur|Il est lisse, un peu frais.
+enfant-m|Le ballon, papa.
+papa|D'accord.
+papa|D'abord le tenir.
+papa|Ensuite rouler.
+maman|Une étape après l'autre.
+narrateur|Victorino pose les deux mains dessus.
+narrateur|Le ballon fait un petit bruit de peau.
+narrateur|Il le fait rouler tout doux, tout près.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tu as fini de rouler ?
+enfant-m|Oui.
+narrateur|Le sable colle un peu aux chaussures.
+narrateur|Le ballon reste à sa place, près de maman.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2430,7 +2517,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Le matin peut encore avancer, au parc. Le banc, le portail, ou le manteau ? On fait l'étape. Une après l'autre.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2598,7 +2685,10 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Le matin peut encore avancer, au parc.
+maman|Le banc, le portail, ou le manteau ?
+papa|On fait l'étape.
+papa|Une après l'autre.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2626,7 +2716,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Tom. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Le banc du parc est en bois clair. Il est un peu froid, encore. Victorino est près du bac à sable. Le ballon vient avec lui. D'abord s'asseoir. Ensuite le goûter. Une étape après l'autre. Victorino s'assoit. Le bois est lisse. Maman sort un morceau de pain. J'ai faim. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le ballon reste rond, tout calme. Un grain de sable brille encore. Loin, la bouilloire de la maison est finie. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2766,7 +2856,25 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Tom. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Le banc du parc est en bois clair.
+narrateur|Il est un peu froid, encore.
+narrateur|Victorino est près du bac à sable.
+narrateur|Le ballon vient avec lui.
+papa|D'abord s'asseoir.
+papa|Ensuite le goûter.
+maman|Une étape après l'autre.
+narrateur|Victorino s'assoit.
+narrateur|Le bois est lisse.
+narrateur|Maman sort un morceau de pain.
+enfant-m|J'ai faim.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as enchaîné le matin.
+narrateur|Le ballon reste rond, tout calme.
+narrateur|Un grain de sable brille encore.
+narrateur|Loin, la bouilloire de la maison est finie.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2794,7 +2902,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le ballon a fait son étape. On s'est assis sur le banc, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2934,7 +3042,13 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le ballon a fait son étape.
+narrateur|On s'est assis sur le banc, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2962,7 +3076,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Léa. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Le portail du parc est vert. Il a une petite barre froide. Victorino est près du bac à sable. Le ballon vient avec lui. D'abord marcher. Ensuite le portail. Une étape après l'autre. Victorino marche. Ses chaussures font toc toc. Papa pose la main sur la barre. On rentre ? Oui. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le ballon reste rond, tout calme. Un grain de sable brille encore. Le portail fait clic, tout doux. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3102,7 +3216,26 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Léa. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Le portail du parc est vert.
+narrateur|Il a une petite barre froide.
+narrateur|Victorino est près du bac à sable.
+narrateur|Le ballon vient avec lui.
+papa|D'abord marcher.
+papa|Ensuite le portail.
+maman|Une étape après l'autre.
+narrateur|Victorino marche.
+narrateur|Ses chaussures font toc toc.
+narrateur|Papa pose la main sur la barre.
+enfant-m|On rentre ?
+papa|Oui.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tu as enchaîné le matin.
+narrateur|Le ballon reste rond, tout calme.
+narrateur|Un grain de sable brille encore.
+narrateur|Le portail fait clic, tout doux.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3130,7 +3263,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le ballon a fait son étape. On a rejoint le portail, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3270,7 +3403,13 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le ballon a fait son étape.
+narrateur|On a rejoint le portail, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3298,7 +3437,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Sami. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Maman tient le manteau, tout près. La fermeture est bleue, un peu froide. Victorino est près du bac à sable. Le ballon vient avec lui. D'abord les bras. Ensuite la fermeture. Une étape après l'autre. Victorino glisse un bras. Puis l'autre. La fermeture monte. Zzz. J'ai chaud. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le ballon reste rond, tout calme. Un grain de sable brille encore. Le manteau sent encore le savon du couloir. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3438,7 +3577,26 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Sami. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Maman tient le manteau, tout près.
+narrateur|La fermeture est bleue, un peu froide.
+narrateur|Victorino est près du bac à sable.
+narrateur|Le ballon vient avec lui.
+maman|D'abord les bras.
+maman|Ensuite la fermeture.
+papa|Une étape après l'autre.
+narrateur|Victorino glisse un bras.
+narrateur|Puis l'autre.
+narrateur|La fermeture monte.
+narrateur|Zzz.
+enfant-m|J'ai chaud.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as enchaîné le matin.
+narrateur|Le ballon reste rond, tout calme.
+narrateur|Un grain de sable brille encore.
+narrateur|Le manteau sent encore le savon du couloir.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3466,7 +3624,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le ballon a fait son étape. On a mis le manteau, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3606,7 +3764,13 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le ballon a fait son étape.
+narrateur|On a mis le manteau, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3634,7 +3798,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
+          <t>Près du bac à sable, le seau jaune attend. L'anse est un peu rêche. Le seau, maman. D'accord. D'abord le prendre. Ensuite le poser. Une étape après l'autre. Victorino prend l'anse à deux mains. Le seau est vide. Il est léger. Il le pose près de ses pieds. Toc. Tu as fait l'étape dite. Bravo. Tu as fini de poser le seau ? Oui, papa. Le sable colle un peu aux chaussures. Le seau reste à sa place, près de papa.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3774,10 +3938,31 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Près du bac à sable, le seau jaune attend.
+narrateur|L'anse est un peu rêche.
+enfant-m|Le seau, maman.
+maman|D'accord.
+maman|D'abord le prendre.
+maman|Ensuite le poser.
+papa|Une étape après l'autre.
+narrateur|Victorino prend l'anse à deux mains.
+narrateur|Le seau est vide.
+narrateur|Il est léger.
+narrateur|Il le pose près de ses pieds.
+narrateur|Toc.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as fini de poser le seau ?
+enfant-m|Oui, papa.
+narrateur|Le sable colle un peu aux chaussures.
+narrateur|Le seau reste à sa place, près de papa.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3802,7 +3987,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Le matin peut encore avancer, au parc. Le banc, le portail, ou le manteau ? On fait l'étape. Une après l'autre.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3970,7 +4155,10 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Le matin peut encore avancer, au parc.
+maman|Le banc, le portail, ou le manteau ?
+papa|On fait l'étape.
+papa|Une après l'autre.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3998,7 +4186,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Tom. La lumière est claire. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Le banc du parc est en bois clair. Il est un peu froid, encore. Victorino est près du bac à sable. Le seau vient avec lui. D'abord s'asseoir. Ensuite le goûter. Une étape après l'autre. Victorino s'assoit. Le bois est lisse. Maman sort une pomme. J'ai faim. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le seau reste jaune, près des pieds. Un grain de sable brille encore. Loin, la bouilloire de la maison est finie. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4138,7 +4326,25 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Tom. La lumière est claire. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Le banc du parc est en bois clair.
+narrateur|Il est un peu froid, encore.
+narrateur|Victorino est près du bac à sable.
+narrateur|Le seau vient avec lui.
+papa|D'abord s'asseoir.
+papa|Ensuite le goûter.
+maman|Une étape après l'autre.
+narrateur|Victorino s'assoit.
+narrateur|Le bois est lisse.
+narrateur|Maman sort une pomme.
+enfant-m|J'ai faim.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as enchaîné le matin.
+narrateur|Le seau reste jaune, près des pieds.
+narrateur|Un grain de sable brille encore.
+narrateur|Loin, la bouilloire de la maison est finie.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4166,7 +4372,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le seau a fait son étape. On s'est assis sur le banc, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4306,7 +4512,13 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le seau a fait son étape.
+narrateur|On s'est assis sur le banc, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4334,7 +4546,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Léa. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Le portail du parc est vert. Il a une petite barre froide. Victorino est près du bac à sable. Le seau vient avec lui. D'abord marcher. Ensuite le portail. Une étape après l'autre. Victorino marche. Ses chaussures font toc toc. Papa pose la main sur la barre. On rentre ? Oui. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le seau reste jaune, près des pieds. Un grain de sable brille encore. Le portail fait clic, tout doux. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4474,7 +4686,26 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Léa. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Le portail du parc est vert.
+narrateur|Il a une petite barre froide.
+narrateur|Victorino est près du bac à sable.
+narrateur|Le seau vient avec lui.
+papa|D'abord marcher.
+papa|Ensuite le portail.
+maman|Une étape après l'autre.
+narrateur|Victorino marche.
+narrateur|Ses chaussures font toc toc.
+narrateur|Papa pose la main sur la barre.
+enfant-m|On rentre ?
+papa|Oui.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tu as enchaîné le matin.
+narrateur|Le seau reste jaune, près des pieds.
+narrateur|Un grain de sable brille encore.
+narrateur|Le portail fait clic, tout doux.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4502,7 +4733,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le seau a fait son étape. On a rejoint le portail, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4642,7 +4873,13 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le seau a fait son étape.
+narrateur|On a rejoint le portail, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4670,7 +4907,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Sami. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Maman tient le manteau, tout près. La fermeture est grise, un peu froide. Victorino est près du bac à sable. Le seau vient avec lui. D'abord les bras. Ensuite la fermeture. Une étape après l'autre. Victorino glisse un bras. Puis l'autre. La fermeture monte. Zzz. J'ai chaud. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le seau reste jaune, près des pieds. Un grain de sable brille encore. Le manteau sent encore le savon du couloir. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4810,7 +5047,26 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Sami. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Maman tient le manteau, tout près.
+narrateur|La fermeture est grise, un peu froide.
+narrateur|Victorino est près du bac à sable.
+narrateur|Le seau vient avec lui.
+maman|D'abord les bras.
+maman|Ensuite la fermeture.
+papa|Une étape après l'autre.
+narrateur|Victorino glisse un bras.
+narrateur|Puis l'autre.
+narrateur|La fermeture monte.
+narrateur|Zzz.
+enfant-m|J'ai chaud.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as enchaîné le matin.
+narrateur|Le seau reste jaune, près des pieds.
+narrateur|Un grain de sable brille encore.
+narrateur|Le manteau sent encore le savon du couloir.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4838,7 +5094,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le seau a fait son étape. On a mis le manteau, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4978,7 +5234,13 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le seau a fait son étape.
+narrateur|On a mis le manteau, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5006,7 +5268,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On range un objet. papa n'est pas loin.</t>
+          <t>Près du bac à sable, le doudou attend dans une poche. Une oreille dépasse, toute douce. Mon doudou. D'accord. D'abord le sortir. Ensuite le tenir. Une étape après l'autre. Victorino sort le doudou. Il sent le savon de la maison. Il le serre contre sa joue. Tu as fait l'étape dite. Bravo. Tu as fini de le sortir ? Oui. Le sable colle un peu aux chaussures. Le doudou reste à sa place, près de maman.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5146,10 +5408,29 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On range un objet. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|Près du bac à sable, le doudou attend dans une poche.
+narrateur|Une oreille dépasse, toute douce.
+enfant-m|Mon doudou.
+maman|D'accord.
+maman|D'abord le sortir.
+maman|Ensuite le tenir.
+papa|Une étape après l'autre.
+narrateur|Victorino sort le doudou.
+narrateur|Il sent le savon de la maison.
+narrateur|Il le serre contre sa joue.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as fini de le sortir ?
+enfant-m|Oui.
+narrateur|Le sable colle un peu aux chaussures.
+narrateur|Le doudou reste à sa place, près de maman.</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5174,7 +5455,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Le matin peut encore avancer, au parc. Le banc, le portail, ou le manteau ? On fait l'étape. Une après l'autre.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5342,7 +5623,10 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Le matin peut encore avancer, au parc.
+maman|Le banc, le portail, ou le manteau ?
+papa|On fait l'étape.
+papa|Une après l'autre.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5370,7 +5654,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Tom. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Le banc du parc est en bois clair. Il est un peu froid, encore. Victorino est près du bac à sable. Le doudou vient avec lui. D'abord s'asseoir. Ensuite le goûter. Une étape après l'autre. Victorino s'assoit. Le bois est lisse. Maman sort un biscuit. J'ai faim. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le doudou reste doux, contre la veste. Un grain de sable brille encore. Loin, la bouilloire de la maison est finie. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5510,7 +5794,25 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Tom. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Le banc du parc est en bois clair.
+narrateur|Il est un peu froid, encore.
+narrateur|Victorino est près du bac à sable.
+narrateur|Le doudou vient avec lui.
+papa|D'abord s'asseoir.
+papa|Ensuite le goûter.
+maman|Une étape après l'autre.
+narrateur|Victorino s'assoit.
+narrateur|Le bois est lisse.
+narrateur|Maman sort un biscuit.
+enfant-m|J'ai faim.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as enchaîné le matin.
+narrateur|Le doudou reste doux, contre la veste.
+narrateur|Un grain de sable brille encore.
+narrateur|Loin, la bouilloire de la maison est finie.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5538,7 +5840,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le doudou a fait son étape. On s'est assis sur le banc, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5678,7 +5980,13 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le doudou a fait son étape.
+narrateur|On s'est assis sur le banc, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5706,7 +6014,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Léa. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Le portail du parc est vert. Il a une petite barre froide. Victorino est près du bac à sable. Le doudou vient avec lui. D'abord marcher. Ensuite le portail. Une étape après l'autre. Victorino marche. Ses chaussures font toc toc. Papa pose la main sur la barre. On rentre ? Oui. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le doudou reste doux, contre la veste. Un grain de sable brille encore. Le portail fait clic, tout doux. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5846,7 +6154,26 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Léa. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Le portail du parc est vert.
+narrateur|Il a une petite barre froide.
+narrateur|Victorino est près du bac à sable.
+narrateur|Le doudou vient avec lui.
+papa|D'abord marcher.
+papa|Ensuite le portail.
+maman|Une étape après l'autre.
+narrateur|Victorino marche.
+narrateur|Ses chaussures font toc toc.
+narrateur|Papa pose la main sur la barre.
+enfant-m|On rentre ?
+papa|Oui.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tu as enchaîné le matin.
+narrateur|Le doudou reste doux, contre la veste.
+narrateur|Un grain de sable brille encore.
+narrateur|Le portail fait clic, tout doux.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5874,7 +6201,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le doudou a fait son étape. On a rejoint le portail, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6014,7 +6341,13 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le doudou a fait son étape.
+narrateur|On a rejoint le portail, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6042,7 +6375,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Sami. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Maman tient le manteau, tout près. La fermeture est verte, un peu froide. Victorino est près du bac à sable. Le doudou vient avec lui. D'abord les bras. Ensuite la fermeture. Une étape après l'autre. Victorino glisse un bras. Puis l'autre. La fermeture monte. Zzz. J'ai chaud. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le doudou reste doux, contre la veste. Un grain de sable brille encore. Le manteau sent encore le savon du couloir. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6182,7 +6515,26 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Sami. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Maman tient le manteau, tout près.
+narrateur|La fermeture est verte, un peu froide.
+narrateur|Victorino est près du bac à sable.
+narrateur|Le doudou vient avec lui.
+maman|D'abord les bras.
+maman|Ensuite la fermeture.
+papa|Une étape après l'autre.
+narrateur|Victorino glisse un bras.
+narrateur|Puis l'autre.
+narrateur|La fermeture monte.
+narrateur|Zzz.
+enfant-m|J'ai chaud.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as enchaîné le matin.
+narrateur|Le doudou reste doux, contre la veste.
+narrateur|Un grain de sable brille encore.
+narrateur|Le manteau sent encore le savon du couloir.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6210,7 +6562,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le doudou a fait son étape. On a mis le manteau, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6350,7 +6702,13 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le doudou a fait son étape.
+narrateur|On a mis le manteau, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6378,7 +6736,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Jules se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
+          <t>Victorino va vers le toboggan. Le métal est un peu froid sous la main. Les marches sont larges, couleur crème. D'abord les marches. Ensuite on glisse. Une étape après l'autre. Je monte. Victorino pose un pied. Puis l'autre. Le vent touche ses cheveux, tout léger. Tu as fait l'étape dite. Bravo. En bas, le tapis de sol est vert. Il sent encore la pluie d'hier. On reste ensemble, près du toboggan. C'est haut, un peu.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6518,11 +6876,29 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Jules va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Jules se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On montre du doigt, sans courir.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Victorino va vers le toboggan.
+narrateur|Le métal est un peu froid sous la main.
+narrateur|Les marches sont larges, couleur crème.
+papa|D'abord les marches.
+papa|Ensuite on glisse.
+maman|Une étape après l'autre.
+enfant-m|Je monte.
+narrateur|Victorino pose un pied.
+narrateur|Puis l'autre.
+narrateur|Le vent touche ses cheveux, tout léger.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+narrateur|En bas, le tapis de sol est vert.
+narrateur|Il sent encore la pluie d'hier.
+maman|On reste ensemble, près du toboggan.
+enfant-m|C'est haut, un peu.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6547,7 +6923,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Enchaîner le matin.</t>
+          <t>Victorino se prépare près du toboggan. On avance comment ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6703,7 +7079,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
+          <t>narrateur|Victorino se prépare près du toboggan.
+maman|On avance comment ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6731,7 +7108,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : faire l'étape dite. Jules respire. Jules retient : une étape après l'autre. On continue, avec maman.</t>
+          <t>Oui. Une étape après l'autre. Tu as fait l'étape dite. Bravo. Le métal du toboggan reste un peu froid. Ensuite, on continue. Oui. On continue, avec nous. C'est plus calme, comme ça.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6875,7 +7252,13 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : faire l'étape dite. Jules respire. Jules retient : une étape après l'autre. On continue, avec maman.</t>
+          <t>papa|Oui. Une étape après l'autre.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+narrateur|Le métal du toboggan reste un peu froid.
+enfant-m|Ensuite, on continue.
+papa|Oui. On continue, avec nous.
+maman|C'est plus calme, comme ça.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6903,7 +7286,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Un objet peut aider le matin, au parc. Le ballon, le seau, ou le doudou ? On prend un objet. Puis l'étape suivante.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7067,7 +7450,10 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Un objet peut aider le matin, au parc.
+papa|Le ballon, le seau, ou le doudou ?
+maman|On prend un objet.
+maman|Puis l'étape suivante.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7095,7 +7481,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le ballon. Un vélo passe au loin. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
+          <t>Près du toboggan, le ballon bleu attend. Il est lisse, un peu frais. Le ballon, papa. D'accord. D'abord le tenir. Ensuite rouler. Une étape après l'autre. Victorino pose les deux mains dessus. Le ballon fait un petit bruit de peau. Il le fait rouler tout doux, tout près. Tu as fait l'étape dite. Bravo. Tu as fini de rouler ? Oui. Le tapis vert est encore un peu humide. Le ballon reste à sa place, près de maman.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7235,10 +7621,29 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le ballon. Un vélo passe au loin. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Près du toboggan, le ballon bleu attend.
+narrateur|Il est lisse, un peu frais.
+enfant-m|Le ballon, papa.
+papa|D'accord.
+papa|D'abord le tenir.
+papa|Ensuite rouler.
+maman|Une étape après l'autre.
+narrateur|Victorino pose les deux mains dessus.
+narrateur|Le ballon fait un petit bruit de peau.
+narrateur|Il le fait rouler tout doux, tout près.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tu as fini de rouler ?
+enfant-m|Oui.
+narrateur|Le tapis vert est encore un peu humide.
+narrateur|Le ballon reste à sa place, près de maman.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7263,7 +7668,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Le matin peut encore avancer, au parc. Le banc, le portail, ou le manteau ? On fait l'étape. Une après l'autre.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7431,7 +7836,10 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Le matin peut encore avancer, au parc.
+maman|Le banc, le portail, ou le manteau ?
+papa|On fait l'étape.
+papa|Une après l'autre.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7459,7 +7867,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Tom. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Le banc du parc est en bois clair. Il est un peu froid, encore. Victorino est près du toboggan. Le ballon vient avec lui. D'abord s'asseoir. Ensuite le goûter. Une étape après l'autre. Victorino s'assoit. Le bois est lisse. Maman sort un morceau de pain. J'ai faim. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le ballon reste rond, tout calme. Le métal du toboggan a séché. Loin, la bouilloire de la maison est finie. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7599,7 +8007,25 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Tom. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Le banc du parc est en bois clair.
+narrateur|Il est un peu froid, encore.
+narrateur|Victorino est près du toboggan.
+narrateur|Le ballon vient avec lui.
+papa|D'abord s'asseoir.
+papa|Ensuite le goûter.
+maman|Une étape après l'autre.
+narrateur|Victorino s'assoit.
+narrateur|Le bois est lisse.
+narrateur|Maman sort un morceau de pain.
+enfant-m|J'ai faim.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as enchaîné le matin.
+narrateur|Le ballon reste rond, tout calme.
+narrateur|Le métal du toboggan a séché.
+narrateur|Loin, la bouilloire de la maison est finie.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7627,7 +8053,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le ballon a fait son étape. On s'est assis sur le banc, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7767,7 +8193,13 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le ballon a fait son étape.
+narrateur|On s'est assis sur le banc, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7795,7 +8227,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Léa. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Le portail du parc est vert. Il a une petite barre froide. Victorino est près du toboggan. Le ballon vient avec lui. D'abord marcher. Ensuite le portail. Une étape après l'autre. Victorino marche. Ses chaussures font toc toc. Papa pose la main sur la barre. On rentre ? Oui. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le ballon reste rond, tout calme. Le métal du toboggan a séché. Le portail fait clic, tout doux. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7935,7 +8367,26 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Léa. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Le portail du parc est vert.
+narrateur|Il a une petite barre froide.
+narrateur|Victorino est près du toboggan.
+narrateur|Le ballon vient avec lui.
+papa|D'abord marcher.
+papa|Ensuite le portail.
+maman|Une étape après l'autre.
+narrateur|Victorino marche.
+narrateur|Ses chaussures font toc toc.
+narrateur|Papa pose la main sur la barre.
+enfant-m|On rentre ?
+papa|Oui.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tu as enchaîné le matin.
+narrateur|Le ballon reste rond, tout calme.
+narrateur|Le métal du toboggan a séché.
+narrateur|Le portail fait clic, tout doux.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7963,7 +8414,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le ballon a fait son étape. On a rejoint le portail, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8103,7 +8554,13 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le ballon a fait son étape.
+narrateur|On a rejoint le portail, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8131,7 +8588,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Sami. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Maman tient le manteau, tout près. La fermeture est bleue, un peu froide. Victorino est près du toboggan. Le ballon vient avec lui. D'abord les bras. Ensuite la fermeture. Une étape après l'autre. Victorino glisse un bras. Puis l'autre. La fermeture monte. Zzz. J'ai chaud. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le ballon reste rond, tout calme. Le métal du toboggan a séché. Le manteau sent encore le savon du couloir. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8271,7 +8728,26 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Sami. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Maman tient le manteau, tout près.
+narrateur|La fermeture est bleue, un peu froide.
+narrateur|Victorino est près du toboggan.
+narrateur|Le ballon vient avec lui.
+maman|D'abord les bras.
+maman|Ensuite la fermeture.
+papa|Une étape après l'autre.
+narrateur|Victorino glisse un bras.
+narrateur|Puis l'autre.
+narrateur|La fermeture monte.
+narrateur|Zzz.
+enfant-m|J'ai chaud.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as enchaîné le matin.
+narrateur|Le ballon reste rond, tout calme.
+narrateur|Le métal du toboggan a séché.
+narrateur|Le manteau sent encore le savon du couloir.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8299,7 +8775,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le ballon a fait son étape. On a mis le manteau, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8439,7 +8915,13 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le ballon a fait son étape.
+narrateur|On a mis le manteau, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8467,7 +8949,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le seau. La lumière est claire. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
+          <t>Près du toboggan, le seau jaune attend. L'anse est un peu rêche. Le seau, maman. D'accord. D'abord le prendre. Ensuite le poser. Une étape après l'autre. Victorino prend l'anse à deux mains. Le seau est vide. Il est léger. Il le pose près de ses pieds. Toc. Tu as fait l'étape dite. Bravo. Tu as fini de poser le seau ? Oui, papa. Le tapis vert est encore un peu humide. Le seau reste à sa place, près de papa.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8607,10 +9089,31 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le seau. La lumière est claire. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Près du toboggan, le seau jaune attend.
+narrateur|L'anse est un peu rêche.
+enfant-m|Le seau, maman.
+maman|D'accord.
+maman|D'abord le prendre.
+maman|Ensuite le poser.
+papa|Une étape après l'autre.
+narrateur|Victorino prend l'anse à deux mains.
+narrateur|Le seau est vide.
+narrateur|Il est léger.
+narrateur|Il le pose près de ses pieds.
+narrateur|Toc.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as fini de poser le seau ?
+enfant-m|Oui, papa.
+narrateur|Le tapis vert est encore un peu humide.
+narrateur|Le seau reste à sa place, près de papa.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8635,7 +9138,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Le matin peut encore avancer, au parc. Le banc, le portail, ou le manteau ? On fait l'étape. Une après l'autre.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8803,7 +9306,10 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Le matin peut encore avancer, au parc.
+maman|Le banc, le portail, ou le manteau ?
+papa|On fait l'étape.
+papa|Une après l'autre.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8831,7 +9337,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Tom. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Le banc du parc est en bois clair. Il est un peu froid, encore. Victorino est près du toboggan. Le seau vient avec lui. D'abord s'asseoir. Ensuite le goûter. Une étape après l'autre. Victorino s'assoit. Le bois est lisse. Maman sort une pomme. J'ai faim. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le seau reste jaune, près des pieds. Le métal du toboggan a séché. Loin, la bouilloire de la maison est finie. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8971,7 +9477,25 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Tom. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Le banc du parc est en bois clair.
+narrateur|Il est un peu froid, encore.
+narrateur|Victorino est près du toboggan.
+narrateur|Le seau vient avec lui.
+papa|D'abord s'asseoir.
+papa|Ensuite le goûter.
+maman|Une étape après l'autre.
+narrateur|Victorino s'assoit.
+narrateur|Le bois est lisse.
+narrateur|Maman sort une pomme.
+enfant-m|J'ai faim.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as enchaîné le matin.
+narrateur|Le seau reste jaune, près des pieds.
+narrateur|Le métal du toboggan a séché.
+narrateur|Loin, la bouilloire de la maison est finie.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -8999,7 +9523,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le seau a fait son étape. On s'est assis sur le banc, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9139,7 +9663,13 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le seau a fait son étape.
+narrateur|On s'est assis sur le banc, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9167,7 +9697,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Léa. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Le portail du parc est vert. Il a une petite barre froide. Victorino est près du toboggan. Le seau vient avec lui. D'abord marcher. Ensuite le portail. Une étape après l'autre. Victorino marche. Ses chaussures font toc toc. Papa pose la main sur la barre. On rentre ? Oui. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le seau reste jaune, près des pieds. Le métal du toboggan a séché. Le portail fait clic, tout doux. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9307,7 +9837,26 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Léa. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Le portail du parc est vert.
+narrateur|Il a une petite barre froide.
+narrateur|Victorino est près du toboggan.
+narrateur|Le seau vient avec lui.
+papa|D'abord marcher.
+papa|Ensuite le portail.
+maman|Une étape après l'autre.
+narrateur|Victorino marche.
+narrateur|Ses chaussures font toc toc.
+narrateur|Papa pose la main sur la barre.
+enfant-m|On rentre ?
+papa|Oui.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tu as enchaîné le matin.
+narrateur|Le seau reste jaune, près des pieds.
+narrateur|Le métal du toboggan a séché.
+narrateur|Le portail fait clic, tout doux.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9335,7 +9884,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le seau a fait son étape. On a rejoint le portail, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9475,7 +10024,13 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le seau a fait son étape.
+narrateur|On a rejoint le portail, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9503,7 +10058,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Sami. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Maman tient le manteau, tout près. La fermeture est grise, un peu froide. Victorino est près du toboggan. Le seau vient avec lui. D'abord les bras. Ensuite la fermeture. Une étape après l'autre. Victorino glisse un bras. Puis l'autre. La fermeture monte. Zzz. J'ai chaud. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le seau reste jaune, près des pieds. Le métal du toboggan a séché. Le manteau sent encore le savon du couloir. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9643,7 +10198,26 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Sami. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Maman tient le manteau, tout près.
+narrateur|La fermeture est grise, un peu froide.
+narrateur|Victorino est près du toboggan.
+narrateur|Le seau vient avec lui.
+maman|D'abord les bras.
+maman|Ensuite la fermeture.
+papa|Une étape après l'autre.
+narrateur|Victorino glisse un bras.
+narrateur|Puis l'autre.
+narrateur|La fermeture monte.
+narrateur|Zzz.
+enfant-m|J'ai chaud.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as enchaîné le matin.
+narrateur|Le seau reste jaune, près des pieds.
+narrateur|Le métal du toboggan a séché.
+narrateur|Le manteau sent encore le savon du couloir.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9671,7 +10245,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le seau a fait son étape. On a mis le manteau, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9811,7 +10385,13 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le seau a fait son étape.
+narrateur|On a mis le manteau, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9839,7 +10419,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le doudou. Il y a des miettes sur la table. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On range un objet. papa n'est pas loin.</t>
+          <t>Près du toboggan, le doudou attend dans une poche. Une oreille dépasse, toute douce. Mon doudou. D'accord. D'abord le sortir. Ensuite le tenir. Une étape après l'autre. Victorino sort le doudou. Il sent le savon de la maison. Il le serre contre sa joue. Tu as fait l'étape dite. Bravo. Tu as fini de le sortir ? Oui. Le tapis vert est encore un peu humide. Le doudou reste à sa place, près de maman.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9979,10 +10559,29 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le doudou. Il y a des miettes sur la table. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On range un objet. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|Près du toboggan, le doudou attend dans une poche.
+narrateur|Une oreille dépasse, toute douce.
+enfant-m|Mon doudou.
+maman|D'accord.
+maman|D'abord le sortir.
+maman|Ensuite le tenir.
+papa|Une étape après l'autre.
+narrateur|Victorino sort le doudou.
+narrateur|Il sent le savon de la maison.
+narrateur|Il le serre contre sa joue.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as fini de le sortir ?
+enfant-m|Oui.
+narrateur|Le tapis vert est encore un peu humide.
+narrateur|Le doudou reste à sa place, près de maman.</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10007,7 +10606,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Le matin peut encore avancer, au parc. Le banc, le portail, ou le manteau ? On fait l'étape. Une après l'autre.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10175,7 +10774,10 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Le matin peut encore avancer, au parc.
+maman|Le banc, le portail, ou le manteau ?
+papa|On fait l'étape.
+papa|Une après l'autre.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10203,7 +10805,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Tom. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Le banc du parc est en bois clair. Il est un peu froid, encore. Victorino est près du toboggan. Le doudou vient avec lui. D'abord s'asseoir. Ensuite le goûter. Une étape après l'autre. Victorino s'assoit. Le bois est lisse. Maman sort un biscuit. J'ai faim. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le doudou reste doux, contre la veste. Le métal du toboggan a séché. Loin, la bouilloire de la maison est finie. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10343,7 +10945,25 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Tom. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Le banc du parc est en bois clair.
+narrateur|Il est un peu froid, encore.
+narrateur|Victorino est près du toboggan.
+narrateur|Le doudou vient avec lui.
+papa|D'abord s'asseoir.
+papa|Ensuite le goûter.
+maman|Une étape après l'autre.
+narrateur|Victorino s'assoit.
+narrateur|Le bois est lisse.
+narrateur|Maman sort un biscuit.
+enfant-m|J'ai faim.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as enchaîné le matin.
+narrateur|Le doudou reste doux, contre la veste.
+narrateur|Le métal du toboggan a séché.
+narrateur|Loin, la bouilloire de la maison est finie.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10371,7 +10991,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le doudou a fait son étape. On s'est assis sur le banc, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10511,7 +11131,13 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le doudou a fait son étape.
+narrateur|On s'est assis sur le banc, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10539,7 +11165,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Léa. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Le portail du parc est vert. Il a une petite barre froide. Victorino est près du toboggan. Le doudou vient avec lui. D'abord marcher. Ensuite le portail. Une étape après l'autre. Victorino marche. Ses chaussures font toc toc. Papa pose la main sur la barre. On rentre ? Oui. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le doudou reste doux, contre la veste. Le métal du toboggan a séché. Le portail fait clic, tout doux. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10679,7 +11305,26 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Léa. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Le portail du parc est vert.
+narrateur|Il a une petite barre froide.
+narrateur|Victorino est près du toboggan.
+narrateur|Le doudou vient avec lui.
+papa|D'abord marcher.
+papa|Ensuite le portail.
+maman|Une étape après l'autre.
+narrateur|Victorino marche.
+narrateur|Ses chaussures font toc toc.
+narrateur|Papa pose la main sur la barre.
+enfant-m|On rentre ?
+papa|Oui.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tu as enchaîné le matin.
+narrateur|Le doudou reste doux, contre la veste.
+narrateur|Le métal du toboggan a séché.
+narrateur|Le portail fait clic, tout doux.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10707,7 +11352,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le doudou a fait son étape. On a rejoint le portail, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10847,7 +11492,13 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le doudou a fait son étape.
+narrateur|On a rejoint le portail, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10875,7 +11526,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Sami. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Maman tient le manteau, tout près. La fermeture est verte, un peu froide. Victorino est près du toboggan. Le doudou vient avec lui. D'abord les bras. Ensuite la fermeture. Une étape après l'autre. Victorino glisse un bras. Puis l'autre. La fermeture monte. Zzz. J'ai chaud. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le doudou reste doux, contre la veste. Le métal du toboggan a séché. Le manteau sent encore le savon du couloir. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11015,7 +11666,26 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Sami. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Maman tient le manteau, tout près.
+narrateur|La fermeture est verte, un peu froide.
+narrateur|Victorino est près du toboggan.
+narrateur|Le doudou vient avec lui.
+maman|D'abord les bras.
+maman|Ensuite la fermeture.
+papa|Une étape après l'autre.
+narrateur|Victorino glisse un bras.
+narrateur|Puis l'autre.
+narrateur|La fermeture monte.
+narrateur|Zzz.
+enfant-m|J'ai chaud.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as enchaîné le matin.
+narrateur|Le doudou reste doux, contre la veste.
+narrateur|Le métal du toboggan a séché.
+narrateur|Le manteau sent encore le savon du couloir.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11043,7 +11713,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le doudou a fait son étape. On a mis le manteau, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11183,7 +11853,13 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le doudou a fait son étape.
+narrateur|On a mis le manteau, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11211,7 +11887,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Jules se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On rit un peu. Je suis là. On reste ensemble.</t>
+          <t>Victorino va vers les balançoires. Les chaînes font un petit bruit de fer. Cling. Cling. Le siège est en bois, un peu lisse. D'abord s'asseoir. Ensuite on balance. Une étape après l'autre. Je m'assois. Victorino s'assoit sur le bois. Il tient les chaînes. Elles sont froides. Tu as fait l'étape dite. Bravo. Le ciel est pâle, au-dessus des arbres. Une feuille tourne, toute seule. On reste ensemble, près des balançoires. Ça va et ça vient.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11351,11 +12027,31 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Jules va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Jules se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On rit un peu.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+          <t>narrateur|Victorino va vers les balançoires.
+narrateur|Les chaînes font un petit bruit de fer.
+narrateur|Cling.
+narrateur|Cling.
+narrateur|Le siège est en bois, un peu lisse.
+papa|D'abord s'asseoir.
+papa|Ensuite on balance.
+maman|Une étape après l'autre.
+enfant-m|Je m'assois.
+narrateur|Victorino s'assoit sur le bois.
+narrateur|Il tient les chaînes.
+narrateur|Elles sont froides.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+narrateur|Le ciel est pâle, au-dessus des arbres.
+narrateur|Une feuille tourne, toute seule.
+maman|On reste ensemble, près des balançoires.
+enfant-m|Ça va et ça vient.</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11380,7 +12076,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Enchaîner le matin.</t>
+          <t>Victorino se prépare près des balançoires. On avance comment ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11536,7 +12232,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
+          <t>narrateur|Victorino se prépare près des balançoires.
+maman|On avance comment ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11564,7 +12261,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : faire l'étape dite. Jules respire. Jules retient : une étape après l'autre. On continue, avec maman.</t>
+          <t>Oui. Une étape après l'autre. Tu as fait l'étape dite. Bravo. Les chaînes se taisent une seconde. Ensuite, on continue. Oui. On continue, avec nous. C'est plus calme, comme ça.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11708,7 +12405,13 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : faire l'étape dite. Jules respire. Jules retient : une étape après l'autre. On continue, avec maman.</t>
+          <t>papa|Oui. Une étape après l'autre.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+narrateur|Les chaînes se taisent une seconde.
+enfant-m|Ensuite, on continue.
+papa|Oui. On continue, avec nous.
+maman|C'est plus calme, comme ça.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11736,7 +12439,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Un objet peut aider le matin, au parc. Le ballon, le seau, ou le doudou ? On prend un objet. Puis l'étape suivante.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11900,7 +12603,10 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Un objet peut aider le matin, au parc.
+papa|Le ballon, le seau, ou le doudou ?
+maman|On prend un objet.
+maman|Puis l'étape suivante.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11928,7 +12634,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
+          <t>Près des balançoires, le ballon jaune attend. Il est lisse, un peu frais. Le ballon, papa. D'accord. D'abord le tenir. Ensuite rouler. Une étape après l'autre. Victorino pose les deux mains dessus. Le ballon fait un petit bruit de peau. Il le fait rouler tout doux, tout près. Tu as fait l'étape dite. Bravo. Tu as fini de rouler ? Oui. L'herbe sous les chaînes est courte. Le ballon reste à sa place, près de maman.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12068,10 +12774,29 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Près des balançoires, le ballon jaune attend.
+narrateur|Il est lisse, un peu frais.
+enfant-m|Le ballon, papa.
+papa|D'accord.
+papa|D'abord le tenir.
+papa|Ensuite rouler.
+maman|Une étape après l'autre.
+narrateur|Victorino pose les deux mains dessus.
+narrateur|Le ballon fait un petit bruit de peau.
+narrateur|Il le fait rouler tout doux, tout près.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tu as fini de rouler ?
+enfant-m|Oui.
+narrateur|L'herbe sous les chaînes est courte.
+narrateur|Le ballon reste à sa place, près de maman.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12096,7 +12821,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Le matin peut encore avancer, au parc. Le banc, le portail, ou le manteau ? On fait l'étape. Une après l'autre.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12264,7 +12989,10 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Le matin peut encore avancer, au parc.
+maman|Le banc, le portail, ou le manteau ?
+papa|On fait l'étape.
+papa|Une après l'autre.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12292,7 +13020,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Tom. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Le banc du parc est en bois clair. Il est un peu froid, encore. Victorino est près des balançoires. Le ballon vient avec lui. D'abord s'asseoir. Ensuite le goûter. Une étape après l'autre. Victorino s'assoit. Le bois est lisse. Maman sort un morceau de pain. J'ai faim. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le ballon reste rond, tout calme. Une chaîne fait un tout petit cling. Loin, la bouilloire de la maison est finie. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12432,7 +13160,25 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Tom. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Le banc du parc est en bois clair.
+narrateur|Il est un peu froid, encore.
+narrateur|Victorino est près des balançoires.
+narrateur|Le ballon vient avec lui.
+papa|D'abord s'asseoir.
+papa|Ensuite le goûter.
+maman|Une étape après l'autre.
+narrateur|Victorino s'assoit.
+narrateur|Le bois est lisse.
+narrateur|Maman sort un morceau de pain.
+enfant-m|J'ai faim.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as enchaîné le matin.
+narrateur|Le ballon reste rond, tout calme.
+narrateur|Une chaîne fait un tout petit cling.
+narrateur|Loin, la bouilloire de la maison est finie.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12460,7 +13206,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le ballon a fait son étape. On s'est assis sur le banc, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12600,7 +13346,13 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le ballon a fait son étape.
+narrateur|On s'est assis sur le banc, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12628,7 +13380,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Léa. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Le portail du parc est vert. Il a une petite barre froide. Victorino est près des balançoires. Le ballon vient avec lui. D'abord marcher. Ensuite le portail. Une étape après l'autre. Victorino marche. Ses chaussures font toc toc. Papa pose la main sur la barre. On rentre ? Oui. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le ballon reste rond, tout calme. Une chaîne fait un tout petit cling. Le portail fait clic, tout doux. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12768,7 +13520,26 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Léa. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Le portail du parc est vert.
+narrateur|Il a une petite barre froide.
+narrateur|Victorino est près des balançoires.
+narrateur|Le ballon vient avec lui.
+papa|D'abord marcher.
+papa|Ensuite le portail.
+maman|Une étape après l'autre.
+narrateur|Victorino marche.
+narrateur|Ses chaussures font toc toc.
+narrateur|Papa pose la main sur la barre.
+enfant-m|On rentre ?
+papa|Oui.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tu as enchaîné le matin.
+narrateur|Le ballon reste rond, tout calme.
+narrateur|Une chaîne fait un tout petit cling.
+narrateur|Le portail fait clic, tout doux.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12796,7 +13567,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le ballon a fait son étape. On a rejoint le portail, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12936,7 +13707,13 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le ballon a fait son étape.
+narrateur|On a rejoint le portail, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12964,7 +13741,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Sami. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Maman tient le manteau, tout près. La fermeture est bleue, un peu froide. Victorino est près des balançoires. Le ballon vient avec lui. D'abord les bras. Ensuite la fermeture. Une étape après l'autre. Victorino glisse un bras. Puis l'autre. La fermeture monte. Zzz. J'ai chaud. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le ballon reste rond, tout calme. Une chaîne fait un tout petit cling. Le manteau sent encore le savon du couloir. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13104,7 +13881,26 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Sami. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Maman tient le manteau, tout près.
+narrateur|La fermeture est bleue, un peu froide.
+narrateur|Victorino est près des balançoires.
+narrateur|Le ballon vient avec lui.
+maman|D'abord les bras.
+maman|Ensuite la fermeture.
+papa|Une étape après l'autre.
+narrateur|Victorino glisse un bras.
+narrateur|Puis l'autre.
+narrateur|La fermeture monte.
+narrateur|Zzz.
+enfant-m|J'ai chaud.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as enchaîné le matin.
+narrateur|Le ballon reste rond, tout calme.
+narrateur|Une chaîne fait un tout petit cling.
+narrateur|Le manteau sent encore le savon du couloir.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13132,7 +13928,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le ballon a fait son étape. On a mis le manteau, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13272,7 +14068,13 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le ballon a fait son étape.
+narrateur|On a mis le manteau, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13300,7 +14102,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
+          <t>Près des balançoires, le seau jaune attend. L'anse est un peu rêche. Le seau, maman. D'accord. D'abord le prendre. Ensuite le poser. Une étape après l'autre. Victorino prend l'anse à deux mains. Le seau est vide. Il est léger. Il le pose près de ses pieds. Toc. Tu as fait l'étape dite. Bravo. Tu as fini de poser le seau ? Oui, papa. L'herbe sous les chaînes est courte. Le seau reste à sa place, près de papa.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13440,10 +14242,31 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Près des balançoires, le seau jaune attend.
+narrateur|L'anse est un peu rêche.
+enfant-m|Le seau, maman.
+maman|D'accord.
+maman|D'abord le prendre.
+maman|Ensuite le poser.
+papa|Une étape après l'autre.
+narrateur|Victorino prend l'anse à deux mains.
+narrateur|Le seau est vide.
+narrateur|Il est léger.
+narrateur|Il le pose près de ses pieds.
+narrateur|Toc.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as fini de poser le seau ?
+enfant-m|Oui, papa.
+narrateur|L'herbe sous les chaînes est courte.
+narrateur|Le seau reste à sa place, près de papa.</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13468,7 +14291,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Le matin peut encore avancer, au parc. Le banc, le portail, ou le manteau ? On fait l'étape. Une après l'autre.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13636,7 +14459,10 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Le matin peut encore avancer, au parc.
+maman|Le banc, le portail, ou le manteau ?
+papa|On fait l'étape.
+papa|Une après l'autre.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13664,7 +14490,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Tom. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Le banc du parc est en bois clair. Il est un peu froid, encore. Victorino est près des balançoires. Le seau vient avec lui. D'abord s'asseoir. Ensuite le goûter. Une étape après l'autre. Victorino s'assoit. Le bois est lisse. Maman sort une pomme. J'ai faim. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le seau reste jaune, près des pieds. Une chaîne fait un tout petit cling. Loin, la bouilloire de la maison est finie. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13804,7 +14630,25 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Tom. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Le banc du parc est en bois clair.
+narrateur|Il est un peu froid, encore.
+narrateur|Victorino est près des balançoires.
+narrateur|Le seau vient avec lui.
+papa|D'abord s'asseoir.
+papa|Ensuite le goûter.
+maman|Une étape après l'autre.
+narrateur|Victorino s'assoit.
+narrateur|Le bois est lisse.
+narrateur|Maman sort une pomme.
+enfant-m|J'ai faim.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as enchaîné le matin.
+narrateur|Le seau reste jaune, près des pieds.
+narrateur|Une chaîne fait un tout petit cling.
+narrateur|Loin, la bouilloire de la maison est finie.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13832,7 +14676,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le seau a fait son étape. On s'est assis sur le banc, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13972,7 +14816,13 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le seau a fait son étape.
+narrateur|On s'est assis sur le banc, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14000,7 +14850,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Léa. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Le portail du parc est vert. Il a une petite barre froide. Victorino est près des balançoires. Le seau vient avec lui. D'abord marcher. Ensuite le portail. Une étape après l'autre. Victorino marche. Ses chaussures font toc toc. Papa pose la main sur la barre. On rentre ? Oui. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le seau reste jaune, près des pieds. Une chaîne fait un tout petit cling. Le portail fait clic, tout doux. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14140,7 +14990,26 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Léa. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Le portail du parc est vert.
+narrateur|Il a une petite barre froide.
+narrateur|Victorino est près des balançoires.
+narrateur|Le seau vient avec lui.
+papa|D'abord marcher.
+papa|Ensuite le portail.
+maman|Une étape après l'autre.
+narrateur|Victorino marche.
+narrateur|Ses chaussures font toc toc.
+narrateur|Papa pose la main sur la barre.
+enfant-m|On rentre ?
+papa|Oui.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tu as enchaîné le matin.
+narrateur|Le seau reste jaune, près des pieds.
+narrateur|Une chaîne fait un tout petit cling.
+narrateur|Le portail fait clic, tout doux.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14168,7 +15037,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le seau a fait son étape. On a rejoint le portail, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14308,7 +15177,13 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le seau a fait son étape.
+narrateur|On a rejoint le portail, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14336,7 +15211,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Sami. La couverture est douce. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Maman tient le manteau, tout près. La fermeture est grise, un peu froide. Victorino est près des balançoires. Le seau vient avec lui. D'abord les bras. Ensuite la fermeture. Une étape après l'autre. Victorino glisse un bras. Puis l'autre. La fermeture monte. Zzz. J'ai chaud. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le seau reste jaune, près des pieds. Une chaîne fait un tout petit cling. Le manteau sent encore le savon du couloir. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14476,7 +15351,26 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Sami. La couverture est douce. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Maman tient le manteau, tout près.
+narrateur|La fermeture est grise, un peu froide.
+narrateur|Victorino est près des balançoires.
+narrateur|Le seau vient avec lui.
+maman|D'abord les bras.
+maman|Ensuite la fermeture.
+papa|Une étape après l'autre.
+narrateur|Victorino glisse un bras.
+narrateur|Puis l'autre.
+narrateur|La fermeture monte.
+narrateur|Zzz.
+enfant-m|J'ai chaud.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as enchaîné le matin.
+narrateur|Le seau reste jaune, près des pieds.
+narrateur|Une chaîne fait un tout petit cling.
+narrateur|Le manteau sent encore le savon du couloir.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14504,7 +15398,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le seau a fait son étape. On a mis le manteau, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14644,7 +15538,13 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le seau a fait son étape.
+narrateur|On a mis le manteau, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14672,7 +15572,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On range un objet. papa n'est pas loin.</t>
+          <t>Près des balançoires, le doudou attend dans une poche. Une oreille dépasse, toute douce. Mon doudou. D'accord. D'abord le sortir. Ensuite le tenir. Une étape après l'autre. Victorino sort le doudou. Il sent le savon de la maison. Il le serre contre sa joue. Tu as fait l'étape dite. Bravo. Tu as fini de le sortir ? Oui. L'herbe sous les chaînes est courte. Le doudou reste à sa place, près de maman.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14812,10 +15712,29 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Jules répète tout bas : une étape après l'autre. On range un objet. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Près des balançoires, le doudou attend dans une poche.
+narrateur|Une oreille dépasse, toute douce.
+enfant-m|Mon doudou.
+maman|D'accord.
+maman|D'abord le sortir.
+maman|Ensuite le tenir.
+papa|Une étape après l'autre.
+narrateur|Victorino sort le doudou.
+narrateur|Il sent le savon de la maison.
+narrateur|Il le serre contre sa joue.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as fini de le sortir ?
+enfant-m|Oui.
+narrateur|L'herbe sous les chaînes est courte.
+narrateur|Le doudou reste à sa place, près de maman.</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14840,7 +15759,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Le matin peut encore avancer, au parc. Le banc, le portail, ou le manteau ? On fait l'étape. Une après l'autre.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15008,7 +15927,10 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Le matin peut encore avancer, au parc.
+maman|Le banc, le portail, ou le manteau ?
+papa|On fait l'étape.
+papa|Une après l'autre.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15036,7 +15958,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Tom. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Le banc du parc est en bois clair. Il est un peu froid, encore. Victorino est près des balançoires. Le doudou vient avec lui. D'abord s'asseoir. Ensuite le goûter. Une étape après l'autre. Victorino s'assoit. Le bois est lisse. Maman sort un biscuit. J'ai faim. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le doudou reste doux, contre la veste. Une chaîne fait un tout petit cling. Loin, la bouilloire de la maison est finie. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15176,7 +16098,25 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Tom. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Tom. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Le banc du parc est en bois clair.
+narrateur|Il est un peu froid, encore.
+narrateur|Victorino est près des balançoires.
+narrateur|Le doudou vient avec lui.
+papa|D'abord s'asseoir.
+papa|Ensuite le goûter.
+maman|Une étape après l'autre.
+narrateur|Victorino s'assoit.
+narrateur|Le bois est lisse.
+narrateur|Maman sort un biscuit.
+enfant-m|J'ai faim.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as enchaîné le matin.
+narrateur|Le doudou reste doux, contre la veste.
+narrateur|Une chaîne fait un tout petit cling.
+narrateur|Loin, la bouilloire de la maison est finie.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15204,7 +16144,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le doudou a fait son étape. On s'est assis sur le banc, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15344,7 +16284,13 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le doudou a fait son étape.
+narrateur|On s'est assis sur le banc, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15372,7 +16318,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Léa. La couverture est douce. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Le portail du parc est vert. Il a une petite barre froide. Victorino est près des balançoires. Le doudou vient avec lui. D'abord marcher. Ensuite le portail. Une étape après l'autre. Victorino marche. Ses chaussures font toc toc. Papa pose la main sur la barre. On rentre ? Oui. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le doudou reste doux, contre la veste. Une chaîne fait un tout petit cling. Le portail fait clic, tout doux. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15512,7 +16458,26 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Léa. La couverture est douce. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Léa. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Le portail du parc est vert.
+narrateur|Il a une petite barre froide.
+narrateur|Victorino est près des balançoires.
+narrateur|Le doudou vient avec lui.
+papa|D'abord marcher.
+papa|Ensuite le portail.
+maman|Une étape après l'autre.
+narrateur|Victorino marche.
+narrateur|Ses chaussures font toc toc.
+narrateur|Papa pose la main sur la barre.
+enfant-m|On rentre ?
+papa|Oui.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tu as enchaîné le matin.
+narrateur|Le doudou reste doux, contre la veste.
+narrateur|Une chaîne fait un tout petit cling.
+narrateur|Le portail fait clic, tout doux.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15540,7 +16505,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le doudou a fait son étape. On a rejoint le portail, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15680,7 +16645,13 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le doudou a fait son étape.
+narrateur|On a rejoint le portail, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15708,7 +16679,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Sami. On entend un oiseau. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>Maman tient le manteau, tout près. La fermeture est verte, un peu froide. Victorino est près des balançoires. Le doudou vient avec lui. D'abord les bras. Ensuite la fermeture. Une étape après l'autre. Victorino glisse un bras. Puis l'autre. La fermeture monte. Zzz. J'ai chaud. Tu as fait l'étape dite. Bravo. Tu as enchaîné le matin. Le doudou reste doux, contre la veste. Une chaîne fait un tout petit cling. Le manteau sent encore le savon du couloir. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15848,7 +16819,26 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint Sami. On entend un oiseau. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Sami. Jules a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Jules a entendu : une étape après l'autre. Jules dit merci à maman. On rentre.</t>
+          <t>narrateur|Maman tient le manteau, tout près.
+narrateur|La fermeture est verte, un peu froide.
+narrateur|Victorino est près des balançoires.
+narrateur|Le doudou vient avec lui.
+maman|D'abord les bras.
+maman|Ensuite la fermeture.
+papa|Une étape après l'autre.
+narrateur|Victorino glisse un bras.
+narrateur|Puis l'autre.
+narrateur|La fermeture monte.
+narrateur|Zzz.
+enfant-m|J'ai chaud.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as enchaîné le matin.
+narrateur|Le doudou reste doux, contre la veste.
+narrateur|Une chaîne fait un tout petit cling.
+narrateur|Le manteau sent encore le savon du couloir.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15876,7 +16866,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bravo, Victorino. Tu as fait du bon travail. Une étape après l'autre. Le doudou a fait son étape. On a mis le manteau, ensemble. Les pois du tapis attendent à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16016,7 +17006,13 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+maman|Une étape après l'autre.
+narrateur|Le doudou a fait son étape.
+narrateur|On a mis le manteau, ensemble.
+narrateur|Les pois du tapis attendent à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16038,7 +17034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16132,6 +17128,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>
